--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>
@@ -82,7 +82,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101,13 +101,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -115,29 +115,15 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1">
-        <v>25</v>
+        <v>324</v>
       </c>
       <c r="C3" s="1">
-        <v>164</v>
+        <v>554</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <v>324</v>
-      </c>
-      <c r="C4" s="1">
-        <v>554</v>
-      </c>
-      <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="68" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="68" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="92" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="92" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="116" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="116" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="156" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="156" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="164" uniqueCount="8">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,12 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="164" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="7">
   <si>
     <t>pull_item</t>
-  </si>
-  <si>
-    <t>beer</t>
   </si>
   <si>
     <t>drinks at restaurant, hotel, cafe, or kiosk</t>
@@ -90,18 +87,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>25</v>
@@ -110,12 +107,12 @@
         <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>324</v>
@@ -124,7 +121,7 @@
         <v>554</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="48" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="72" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="144" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>
@@ -118,7 +118,7 @@
         <v>324</v>
       </c>
       <c r="C3" s="1">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="144" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="152" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="152" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="160" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="160" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="168" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="176" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="176" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="192" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="192" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="200" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="200" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="216" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="216" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="224" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="224" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="232" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="232" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="248" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="248" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="256" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="256" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="304" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="304" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="312" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="312" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="328" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="328" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="336" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="336" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="344" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="344" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="368" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="368" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="368" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="376" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="400" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="400" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="408" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="408" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="416" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="416" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="432" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="432" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="456" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>

--- a/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
+++ b/outputs/master_rename_build/tables/mixed_dimension_no_verdict.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="456" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="472" uniqueCount="7">
   <si>
     <t>pull_item</t>
   </si>
